--- a/data/trans_orig/RUIDO_1-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/RUIDO_1-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según lo que estaría dispuesta a pagar al año para que la administración pública ponga en marcha actuaciones (+++) en su municipio/ciudad (o lugar de residencia) que haga reducir la contaminación del ruido en 2023</t>
+          <t>Población según lo que estaría dispuesta a pagar al año para que la administración pública ponga en marcha actuaciones (+++) en su municipio/ciudad (o lugar de residencia) que haga reducir la contaminación del ruido en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4840</t>
+          <t>5232</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4870</t>
+          <t>4832</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>668</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6851</t>
+          <t>6657</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9064</t>
+          <t>7859</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3670</t>
+          <t>3517</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>675</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8892</t>
+          <t>9357</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -956,97 +956,97 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1625</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="R6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>1003</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>1239</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1069,82 +1069,82 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>756</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1625</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3712</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>756</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4569</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>756</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>3832</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7238</t>
+          <t>7230</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1846</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8357</t>
+          <t>8075</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2989</t>
+          <t>3103</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>12508</t>
+          <t>11514</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26520</t>
+          <t>25340</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3225</t>
+          <t>3527</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>25736</t>
+          <t>26703</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -1408,12 +1408,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>1960</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11460</t>
+          <t>11376</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1443,12 +1443,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2731</t>
+          <t>2651</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10580</t>
+          <t>11200</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1478,12 +1478,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6172</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18381</t>
+          <t>19534</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -1521,12 +1521,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1375</t>
+          <t>1154</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11082</t>
+          <t>10240</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1536,12 +1536,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1556,12 +1556,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1194</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6481</t>
+          <t>6563</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1571,12 +1571,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3531</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>12929</t>
+          <t>13480</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1606,12 +1606,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -1634,12 +1634,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7419</t>
+          <t>7587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>25040</t>
+          <t>25345</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1649,12 +1649,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1669,12 +1669,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>14731</t>
+          <t>14695</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>28696</t>
+          <t>29066</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1684,12 +1684,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>25675</t>
+          <t>25005</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>47364</t>
+          <t>47529</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1719,12 +1719,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,76%</t>
         </is>
       </c>
     </row>
@@ -1747,12 +1747,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>43108</t>
+          <t>42262</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>70255</t>
+          <t>68733</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1782,12 +1782,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30045</t>
+          <t>30398</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>48216</t>
+          <t>47880</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1817,12 +1817,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>79213</t>
+          <t>79315</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>111706</t>
+          <t>111174</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,82%</t>
         </is>
       </c>
     </row>
@@ -1860,12 +1860,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>238387</t>
+          <t>240882</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>274837</t>
+          <t>276430</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>69,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>79,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1895,12 +1895,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>266049</t>
+          <t>265785</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>289868</t>
+          <t>289707</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>74,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>81,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1930,12 +1930,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>513312</t>
+          <t>515266</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>557205</t>
+          <t>557846</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>73,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,38%</t>
         </is>
       </c>
     </row>
@@ -2095,7 +2095,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9733</t>
+          <t>9654</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7475</t>
+          <t>7500</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1333</t>
+          <t>1588</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13912</t>
+          <t>12935</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -2203,12 +2203,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>714</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9275</t>
+          <t>9409</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2238,12 +2238,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1218</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2273,12 +2273,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>718</t>
+          <t>754</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9106</t>
+          <t>8656</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5808</t>
+          <t>6455</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>3708</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6985</t>
+          <t>5965</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,61%</t>
         </is>
       </c>
     </row>
@@ -2429,97 +2429,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>1918</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5513</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>1066</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>6123</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>6461</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,11%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1066</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>5379</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,11%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -2542,12 +2542,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1841</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12755</t>
+          <t>12741</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6695</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2612,12 +2612,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>2340</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>15008</t>
+          <t>14192</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6194</t>
+          <t>6858</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2614</t>
+          <t>3059</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2725,12 +2725,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>462</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>7139</t>
+          <t>7058</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
     </row>
@@ -2768,12 +2768,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5125</t>
+          <t>5012</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27031</t>
+          <t>28326</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2783,12 +2783,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7785</t>
+          <t>7977</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>27390</t>
+          <t>27413</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>16972</t>
+          <t>16647</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>44652</t>
+          <t>45290</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -2881,12 +2881,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>7330</t>
+          <t>6502</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>29212</t>
+          <t>26555</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>636</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5688</t>
+          <t>6159</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>8099</t>
+          <t>8693</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>28970</t>
+          <t>29749</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2966,12 +2966,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -2994,12 +2994,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>24565</t>
+          <t>23938</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>58348</t>
+          <t>58980</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3009,12 +3009,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>20509</t>
+          <t>20908</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>37565</t>
+          <t>37937</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>49608</t>
+          <t>51115</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>87865</t>
+          <t>89870</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,18%</t>
         </is>
       </c>
     </row>
@@ -3107,12 +3107,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>43462</t>
+          <t>42327</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>69932</t>
+          <t>72220</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3122,12 +3122,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3142,12 +3142,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>45844</t>
+          <t>46130</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>69587</t>
+          <t>69851</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>95339</t>
+          <t>94257</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>131483</t>
+          <t>130654</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,34%</t>
         </is>
       </c>
     </row>
@@ -3220,12 +3220,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>339945</t>
+          <t>342050</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>389436</t>
+          <t>388859</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3235,12 +3235,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>68,35%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>351231</t>
+          <t>352717</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>385386</t>
+          <t>386140</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>73,65%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>80,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>708397</t>
+          <t>706885</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>765394</t>
+          <t>763070</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>72,18%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>77,92%</t>
         </is>
       </c>
     </row>
@@ -3450,12 +3450,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2286</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>11956</t>
+          <t>11286</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3465,12 +3465,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5894</t>
+          <t>5892</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2556</t>
+          <t>2899</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>14798</t>
+          <t>16097</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3535,12 +3535,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -3563,12 +3563,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>162</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>8349</t>
+          <t>7309</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3598,12 +3598,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>843</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>11812</t>
+          <t>12422</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3613,12 +3613,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3633,12 +3633,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2893</t>
+          <t>2624</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>15415</t>
+          <t>15232</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3648,12 +3648,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -3676,97 +3676,97 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>2354</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>1988</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>10160</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>1,87%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="R30" s="2" t="inlineStr">
         <is>
           <t>2354</t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr">
+      <c r="S30" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>10377</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>10859</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>1,91%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>2354</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>9780</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -3789,97 +3789,97 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>1988</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
+      <c r="R31" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>2187</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t>2111</t>
-        </is>
-      </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3902,12 +3902,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>8754</t>
+          <t>9613</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3917,12 +3917,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>837</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>11604</t>
+          <t>11428</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>3040</t>
+          <t>2958</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>16178</t>
+          <t>17155</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -4015,12 +4015,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>3193</t>
+          <t>3256</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>15483</t>
+          <t>16327</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4030,12 +4030,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>351</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>7132</t>
+          <t>8031</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>3850</t>
+          <t>3673</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>18842</t>
+          <t>19308</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -4128,12 +4128,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1427</t>
+          <t>1354</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>27048</t>
+          <t>22431</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4143,12 +4143,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>9078</t>
+          <t>9526</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>156347</t>
+          <t>161685</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>14990</t>
+          <t>14799</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>170525</t>
+          <t>169881</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,39%</t>
         </is>
       </c>
     </row>
@@ -4241,12 +4241,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>6351</t>
+          <t>6537</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>20223</t>
+          <t>20579</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4256,12 +4256,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4276,12 +4276,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1833</t>
+          <t>2110</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>16645</t>
+          <t>17150</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4291,12 +4291,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4311,12 +4311,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>8843</t>
+          <t>9236</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>32269</t>
+          <t>32310</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -4354,12 +4354,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>17568</t>
+          <t>16949</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>42500</t>
+          <t>41347</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4369,12 +4369,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>4062</t>
+          <t>4579</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>25801</t>
+          <t>26836</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4404,12 +4404,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>18668</t>
+          <t>18697</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>61708</t>
+          <t>62115</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,09%</t>
         </is>
       </c>
     </row>
@@ -4467,12 +4467,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>12293</t>
+          <t>12106</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>35616</t>
+          <t>35495</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>8282</t>
+          <t>9373</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>53817</t>
+          <t>53691</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4517,12 +4517,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>23114</t>
+          <t>22761</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>73906</t>
+          <t>74563</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4552,12 +4552,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,51%</t>
         </is>
       </c>
     </row>
@@ -4580,12 +4580,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>225188</t>
+          <t>226590</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>263784</t>
+          <t>263843</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>68,36%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>334055</t>
+          <t>334280</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>505347</t>
+          <t>505638</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>61,39%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>584534</t>
+          <t>588003</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>781890</t>
+          <t>777026</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>67,13%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>88,7%</t>
         </is>
       </c>
     </row>
@@ -4810,97 +4810,97 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>1363</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>1705</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>4514</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K40" s="2" t="inlineStr">
+      <c r="R40" s="2" t="inlineStr">
         <is>
           <t>1363</t>
         </is>
       </c>
-      <c r="L40" s="2" t="inlineStr">
+      <c r="S40" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>4774</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>4157</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>1363</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T40" s="2" t="inlineStr">
-        <is>
-          <t>4688</t>
-        </is>
-      </c>
-      <c r="U40" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,41%</t>
         </is>
       </c>
     </row>
@@ -4923,12 +4923,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>2483</t>
+          <t>2072</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>12460</t>
+          <t>11579</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4958,12 +4958,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>7342</t>
+          <t>7922</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4993,12 +4993,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>4314</t>
+          <t>4872</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>15384</t>
+          <t>15132</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5008,12 +5008,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -5041,7 +5041,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>4999</t>
+          <t>7011</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5071,62 +5071,62 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>1329</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>1218</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>6535</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>0,13%</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t>1329</t>
-        </is>
-      </c>
-      <c r="S42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T42" s="2" t="inlineStr">
-        <is>
-          <t>5970</t>
-        </is>
-      </c>
-      <c r="U42" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="V42" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,65%</t>
         </is>
       </c>
     </row>
@@ -5149,97 +5149,97 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>659</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>1705</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>3802</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>0,12%</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>0,72%</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K43" s="2" t="inlineStr">
+      <c r="R43" s="2" t="inlineStr">
         <is>
           <t>659</t>
         </is>
       </c>
-      <c r="L43" s="2" t="inlineStr">
+      <c r="S43" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>3278</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>2687</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>0,07%</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t>659</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T43" s="2" t="inlineStr">
-        <is>
-          <t>3391</t>
-        </is>
-      </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
-      <c r="V43" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,27%</t>
         </is>
       </c>
     </row>
@@ -5262,12 +5262,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>1065</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>9410</t>
+          <t>9321</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1557</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>9021</t>
+          <t>9333</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>4209</t>
+          <t>3983</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>14038</t>
+          <t>14340</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -5375,12 +5375,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>1807</t>
+          <t>1836</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>12740</t>
+          <t>12986</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5390,12 +5390,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>3111</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>12331</t>
+          <t>13419</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5425,12 +5425,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>6444</t>
+          <t>6003</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>20207</t>
+          <t>19916</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -5488,12 +5488,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>3107</t>
+          <t>3012</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>13553</t>
+          <t>13108</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5503,12 +5503,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>2688</t>
+          <t>2921</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>14760</t>
+          <t>15940</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5538,12 +5538,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>7692</t>
+          <t>7911</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>22854</t>
+          <t>22824</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5573,7 +5573,7 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5601,12 +5601,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>1110</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>8651</t>
+          <t>8385</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5616,12 +5616,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5636,12 +5636,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>1222</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>7193</t>
+          <t>7226</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>2722</t>
+          <t>2941</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>12359</t>
+          <t>11587</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5686,12 +5686,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -5714,12 +5714,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>5396</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>40989</t>
+          <t>35012</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5729,12 +5729,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5749,12 +5749,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>5961</t>
+          <t>6354</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>16488</t>
+          <t>16916</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5764,12 +5764,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>14133</t>
+          <t>14918</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>43986</t>
+          <t>45688</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5799,12 +5799,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,55%</t>
         </is>
       </c>
     </row>
@@ -5827,12 +5827,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>46714</t>
+          <t>46498</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>74319</t>
+          <t>75244</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5862,12 +5862,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>45794</t>
+          <t>46371</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>70508</t>
+          <t>69832</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5877,12 +5877,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>99903</t>
+          <t>100631</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>134421</t>
+          <t>134594</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5912,12 +5912,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,4%</t>
         </is>
       </c>
     </row>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>355575</t>
+          <t>355807</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>393527</t>
+          <t>394792</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>74,87%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>83,08%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5975,12 +5975,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>420785</t>
+          <t>419371</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>451618</t>
+          <t>450684</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -5990,12 +5990,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6010,12 +6010,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>787554</t>
+          <t>788881</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>834280</t>
+          <t>835607</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6025,12 +6025,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>83,16%</t>
         </is>
       </c>
     </row>
@@ -6170,12 +6170,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>4337</t>
+          <t>3738</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>17622</t>
+          <t>16767</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6185,12 +6185,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>3435</t>
+          <t>3449</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>13227</t>
+          <t>14189</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6225,7 +6225,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>9670</t>
+          <t>9608</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>26502</t>
+          <t>26465</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>7141</t>
+          <t>6786</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>22584</t>
+          <t>22049</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6318,12 +6318,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>4886</t>
+          <t>4928</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>16324</t>
+          <t>16392</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6353,12 +6353,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>13907</t>
+          <t>14481</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>31692</t>
+          <t>33378</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6368,12 +6368,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -6396,12 +6396,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>167</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>8168</t>
+          <t>8988</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>637</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>10765</t>
+          <t>10337</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6451,7 +6451,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6466,12 +6466,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>1770</t>
+          <t>1856</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>13259</t>
+          <t>12607</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,35%</t>
         </is>
       </c>
     </row>
@@ -6509,12 +6509,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>1802</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>660</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>7115</t>
+          <t>7724</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6564,7 +6564,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6579,12 +6579,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>656</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>8399</t>
+          <t>6895</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,19%</t>
         </is>
       </c>
     </row>
@@ -6622,12 +6622,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>8648</t>
+          <t>8190</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>25575</t>
+          <t>24974</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6657,12 +6657,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>8280</t>
+          <t>8655</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>22208</t>
+          <t>22806</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6672,12 +6672,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6692,12 +6692,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>20225</t>
+          <t>19392</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>41402</t>
+          <t>41985</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6707,12 +6707,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>11469</t>
+          <t>11207</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>40562</t>
+          <t>39914</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6770,12 +6770,12 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>17274</t>
+          <t>17883</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6785,12 +6785,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6805,12 +6805,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>19008</t>
+          <t>19808</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>49739</t>
+          <t>51708</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -6820,12 +6820,12 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -6848,12 +6848,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>19410</t>
+          <t>18591</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>49238</t>
+          <t>50759</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -6863,12 +6863,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>36493</t>
+          <t>35369</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>219719</t>
+          <t>188811</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6918,12 +6918,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>65841</t>
+          <t>65088</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>222454</t>
+          <t>259745</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>7,29%</t>
         </is>
       </c>
     </row>
@@ -6961,12 +6961,12 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>21975</t>
+          <t>21897</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>50961</t>
+          <t>46900</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -6976,12 +6976,12 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -6996,12 +6996,12 @@
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>10336</t>
+          <t>10040</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>24890</t>
+          <t>24483</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7011,12 +7011,12 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7031,12 +7031,12 @@
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>37181</t>
+          <t>37468</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>67932</t>
+          <t>67960</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7074,12 +7074,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>70481</t>
+          <t>71986</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>123487</t>
+          <t>121176</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7089,12 +7089,12 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7109,12 +7109,12 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>50614</t>
+          <t>52719</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>90751</t>
+          <t>90402</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7124,12 +7124,12 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7144,12 +7144,12 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>130996</t>
+          <t>130783</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>198483</t>
+          <t>200021</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -7187,12 +7187,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>163434</t>
+          <t>164745</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>214241</t>
+          <t>218285</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7202,12 +7202,12 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>126074</t>
+          <t>129541</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>213934</t>
+          <t>213533</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7237,12 +7237,12 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7257,12 +7257,12 @@
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>301026</t>
+          <t>303378</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>413309</t>
+          <t>412655</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -7272,12 +7272,12 @@
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,58%</t>
         </is>
       </c>
     </row>
@@ -7300,12 +7300,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>1208325</t>
+          <t>1204150</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>1287758</t>
+          <t>1291266</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7315,12 +7315,12 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>72,76%</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7335,12 +7335,12 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>1434953</t>
+          <t>1435429</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>1631081</t>
+          <t>1623612</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7350,12 +7350,12 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>75,24%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,1%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7370,12 +7370,12 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>2679933</t>
+          <t>2672528</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>2910240</t>
+          <t>2904034</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -7385,12 +7385,12 @@
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>75,01%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>81,51%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/RUIDO_1-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/RUIDO_1-Habitat-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>960</t>
+          <t>885</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5232</t>
+          <t>4907</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1791</t>
+          <t>1855</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>462</t>
+          <t>468</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4832</t>
+          <t>5617</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2751</t>
+          <t>2740</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>818</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6657</t>
+          <t>7349</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2315</t>
+          <t>2443</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7859</t>
+          <t>8815</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>710</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3517</t>
+          <t>3616</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>3002</t>
+          <t>3153</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>717</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9357</t>
+          <t>8795</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>756</t>
+          <t>809</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3712</t>
+          <t>4212</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>756</t>
+          <t>809</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3832</t>
+          <t>4077</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2051</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7230</t>
+          <t>8797</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>4297</t>
+          <t>5156</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2518</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8075</t>
+          <t>9619</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>6348</t>
+          <t>7541</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3103</t>
+          <t>3553</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>11514</t>
+          <t>13702</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5059</t>
+          <t>4408</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1300,12 +1300,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25340</t>
+          <t>22670</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>688</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3527</t>
+          <t>3954</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>5696</t>
+          <t>5096</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
@@ -1370,12 +1370,12 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>26703</t>
+          <t>23127</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -1403,32 +1403,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5072</t>
+          <t>5842</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1960</t>
+          <t>2322</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11376</t>
+          <t>12706</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1438,32 +1438,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>5799</t>
+          <t>5973</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2651</t>
+          <t>2668</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11200</t>
+          <t>11263</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1473,32 +1473,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>10871</t>
+          <t>11814</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>6423</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19534</t>
+          <t>20471</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -1516,32 +1516,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4007</t>
+          <t>4801</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1154</t>
+          <t>1619</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10240</t>
+          <t>11637</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1551,32 +1551,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3098</t>
+          <t>3708</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1602</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6563</t>
+          <t>7362</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1586,32 +1586,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>7105</t>
+          <t>8510</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>4698</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>13480</t>
+          <t>15517</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -1629,32 +1629,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>14171</t>
+          <t>17262</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7587</t>
+          <t>9497</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>25345</t>
+          <t>28667</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1664,32 +1664,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>20904</t>
+          <t>22920</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>14695</t>
+          <t>15960</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>29066</t>
+          <t>30619</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1699,32 +1699,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>35076</t>
+          <t>40182</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>25005</t>
+          <t>29309</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>47529</t>
+          <t>53556</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>7,06%</t>
         </is>
       </c>
     </row>
@@ -1742,32 +1742,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>54727</t>
+          <t>56408</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42262</t>
+          <t>43456</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>68733</t>
+          <t>71341</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1777,32 +1777,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>38776</t>
+          <t>40949</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30398</t>
+          <t>31920</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47880</t>
+          <t>50669</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1812,32 +1812,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>93502</t>
+          <t>97357</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>79315</t>
+          <t>82636</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>111174</t>
+          <t>114569</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,1%</t>
         </is>
       </c>
     </row>
@@ -1855,32 +1855,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>259609</t>
+          <t>282977</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>240882</t>
+          <t>260949</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>276430</t>
+          <t>299898</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>74,98%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>69,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1890,32 +1890,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>278025</t>
+          <t>298623</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>265785</t>
+          <t>285448</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>289707</t>
+          <t>311038</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>78,37%</t>
+          <t>78,3%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,92%</t>
+          <t>74,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1925,32 +1925,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>537635</t>
+          <t>581600</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>515266</t>
+          <t>557677</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>557846</t>
+          <t>601335</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>76,65%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>79,25%</t>
         </is>
       </c>
     </row>
@@ -1968,17 +1968,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>347971</t>
+          <t>377410</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>347971</t>
+          <t>377410</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>347971</t>
+          <t>377410</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2003,17 +2003,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>354770</t>
+          <t>381392</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>354770</t>
+          <t>381392</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>354770</t>
+          <t>381392</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2038,17 +2038,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>702742</t>
+          <t>758802</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>702742</t>
+          <t>758802</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>702742</t>
+          <t>758802</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2625</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2095,12 +2095,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9654</t>
+          <t>12747</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2206</t>
+          <t>2319</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7500</t>
+          <t>8834</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,17 +2155,17 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>4831</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1588</t>
+          <t>1695</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12935</t>
+          <t>16220</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -2198,17 +2198,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2979</t>
+          <t>3246</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>714</t>
+          <t>810</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9409</t>
+          <t>9692</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2218,12 +2218,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2268,17 +2268,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>2979</t>
+          <t>3246</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>812</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8656</t>
+          <t>9014</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>1189</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2321,12 +2321,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6455</t>
+          <t>6050</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>692</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3708</t>
+          <t>4171</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1777</t>
+          <t>1881</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5965</t>
+          <t>7000</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>1086</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5513</t>
+          <t>6177</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>1086</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6461</t>
+          <t>5516</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -2537,32 +2537,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>5121</t>
+          <t>5242</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>1191</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12741</t>
+          <t>13482</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1632</t>
+          <t>1614</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>5714</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2607,32 +2607,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>6753</t>
+          <t>6856</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2340</t>
+          <t>2096</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14192</t>
+          <t>14811</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -2650,7 +2650,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1954</t>
+          <t>1774</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2660,12 +2660,12 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6858</t>
+          <t>6188</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>471</t>
+          <t>502</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3059</t>
+          <t>2762</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2720,22 +2720,22 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>2424</t>
+          <t>2276</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>462</t>
+          <t>498</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>7058</t>
+          <t>7137</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -2763,32 +2763,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>12085</t>
+          <t>12858</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5012</t>
+          <t>5557</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>28326</t>
+          <t>30321</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2798,32 +2798,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>14718</t>
+          <t>15762</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7977</t>
+          <t>8197</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>27413</t>
+          <t>28243</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2833,32 +2833,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>26804</t>
+          <t>28620</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>16647</t>
+          <t>17201</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>45290</t>
+          <t>46999</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -2876,32 +2876,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>14052</t>
+          <t>14478</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6502</t>
+          <t>6675</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>26555</t>
+          <t>28928</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2594</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>724</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6159</t>
+          <t>5965</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>16464</t>
+          <t>17072</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>8693</t>
+          <t>9476</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>29749</t>
+          <t>33328</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -2989,32 +2989,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>38431</t>
+          <t>38011</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>23938</t>
+          <t>25161</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>58980</t>
+          <t>57077</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3024,32 +3024,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>28291</t>
+          <t>30726</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>20908</t>
+          <t>22777</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>37937</t>
+          <t>40385</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3059,32 +3059,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>66722</t>
+          <t>68738</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>51115</t>
+          <t>53031</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>89870</t>
+          <t>89697</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>8,4%</t>
         </is>
       </c>
     </row>
@@ -3102,32 +3102,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>54887</t>
+          <t>58718</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>42327</t>
+          <t>45331</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>72220</t>
+          <t>74203</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3137,32 +3137,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>56509</t>
+          <t>60884</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>46130</t>
+          <t>49140</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>69851</t>
+          <t>73439</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3172,27 +3172,27 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>111395</t>
+          <t>119602</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>94257</t>
+          <t>103369</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>130654</t>
+          <t>142373</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3215,32 +3215,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>367158</t>
+          <t>398576</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>342050</t>
+          <t>372176</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>388859</t>
+          <t>418935</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>73,37%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>68,35%</t>
+          <t>69,31%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3250,32 +3250,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>370976</t>
+          <t>414116</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>352717</t>
+          <t>395026</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>386140</t>
+          <t>430825</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>78,09%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>74,49%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3285,32 +3285,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>738135</t>
+          <t>812692</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>706885</t>
+          <t>782137</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>763070</t>
+          <t>840532</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>75,37%</t>
+          <t>76,15%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>72,18%</t>
+          <t>73,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>78,75%</t>
         </is>
       </c>
     </row>
@@ -3328,17 +3328,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>500419</t>
+          <t>536982</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>500419</t>
+          <t>536982</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>500419</t>
+          <t>536982</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,17 +3363,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>478930</t>
+          <t>530296</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>478930</t>
+          <t>530296</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>478930</t>
+          <t>530296</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,17 +3398,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>979350</t>
+          <t>1067278</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>979350</t>
+          <t>1067278</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>979350</t>
+          <t>1067278</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3445,102 +3445,102 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>5482</t>
+          <t>7799</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2286</t>
+          <t>3311</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>11286</t>
+          <t>14792</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
+          <t>0,88%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>3,95%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>2031</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>604</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>5389</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>9831</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>5114</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>17545</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>1,33%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
           <t>0,69%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>3,41%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>5892</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>7481</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>2899</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>16097</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -3558,32 +3558,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2261</t>
+          <t>4573</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>877</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7309</t>
+          <t>13831</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3593,32 +3593,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>6143</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>2757</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>12422</t>
+          <t>11258</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3628,32 +3628,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>7541</t>
+          <t>10716</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2624</t>
+          <t>5452</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>15232</t>
+          <t>20984</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2354</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>10160</t>
+          <t>6822</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>2354</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>10859</t>
+          <t>8139</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -3897,32 +3897,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>3763</t>
+          <t>3961</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>980</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>9613</t>
+          <t>9206</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3932,32 +3932,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>4297</t>
+          <t>4769</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>837</t>
+          <t>1838</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>11428</t>
+          <t>11262</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3967,32 +3967,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>8060</t>
+          <t>8729</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2958</t>
+          <t>4134</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>17155</t>
+          <t>16178</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -4010,32 +4010,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>7540</t>
+          <t>7666</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>3256</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>16327</t>
+          <t>14466</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4045,32 +4045,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>2829</t>
+          <t>2915</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>762</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>8031</t>
+          <t>7073</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4080,32 +4080,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>10369</t>
+          <t>10580</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>3673</t>
+          <t>5579</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>19308</t>
+          <t>19586</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -4123,32 +4123,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>6823</t>
+          <t>7018</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1354</t>
+          <t>2085</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>22099</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4158,32 +4158,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>47009</t>
+          <t>16878</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>9526</t>
+          <t>9842</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>161685</t>
+          <t>27992</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4193,32 +4193,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>53832</t>
+          <t>23896</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>14799</t>
+          <t>13688</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>169881</t>
+          <t>38734</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -4241,27 +4241,27 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>6537</t>
+          <t>6573</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>20579</t>
+          <t>20872</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4271,32 +4271,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>8369</t>
+          <t>9388</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>2110</t>
+          <t>5299</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>17150</t>
+          <t>15140</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4306,32 +4306,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>20304</t>
+          <t>21324</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>9236</t>
+          <t>13893</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>32310</t>
+          <t>31118</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -4349,32 +4349,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>27320</t>
+          <t>33427</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>16949</t>
+          <t>21992</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>41347</t>
+          <t>51340</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4384,32 +4384,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>14009</t>
+          <t>21268</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>4579</t>
+          <t>13850</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>26836</t>
+          <t>31084</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4419,32 +4419,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>41328</t>
+          <t>54695</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>18697</t>
+          <t>39089</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>62115</t>
+          <t>71398</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>9,66%</t>
         </is>
       </c>
     </row>
@@ -4462,32 +4462,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>20319</t>
+          <t>25002</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>12106</t>
+          <t>15385</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>35495</t>
+          <t>39539</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4497,32 +4497,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>29251</t>
+          <t>33336</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>9373</t>
+          <t>22618</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>53691</t>
+          <t>48342</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4532,32 +4532,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>49570</t>
+          <t>58338</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>22761</t>
+          <t>43631</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>74563</t>
+          <t>76883</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>10,4%</t>
         </is>
       </c>
     </row>
@@ -4575,32 +4575,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>246001</t>
+          <t>272869</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>226590</t>
+          <t>250843</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>263843</t>
+          <t>291913</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>72,91%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>67,03%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4610,32 +4610,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>429138</t>
+          <t>266241</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>334280</t>
+          <t>249717</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>505638</t>
+          <t>281762</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>72,97%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>61,39%</t>
+          <t>68,44%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>77,22%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4645,32 +4645,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>675139</t>
+          <t>539110</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>588003</t>
+          <t>514341</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>777026</t>
+          <t>565917</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>72,94%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>67,13%</t>
+          <t>69,59%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>76,57%</t>
         </is>
       </c>
     </row>
@@ -4688,17 +4688,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>331443</t>
+          <t>374250</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>331443</t>
+          <t>374250</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>331443</t>
+          <t>374250</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4723,17 +4723,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>544536</t>
+          <t>364873</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>544536</t>
+          <t>364873</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>544536</t>
+          <t>364873</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4758,17 +4758,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>875979</t>
+          <t>739123</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>875979</t>
+          <t>739123</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>875979</t>
+          <t>739123</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4840,7 +4840,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>1363</t>
+          <t>1410</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -4850,12 +4850,12 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>4514</t>
+          <t>4976</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
@@ -4865,7 +4865,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>1363</t>
+          <t>1410</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>4157</t>
+          <t>4963</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
@@ -4900,7 +4900,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,45%</t>
         </is>
       </c>
     </row>
@@ -4918,32 +4918,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>5405</t>
+          <t>5251</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>2072</t>
+          <t>1881</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>11579</t>
+          <t>10781</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4953,32 +4953,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>3318</t>
+          <t>3488</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>1340</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>7922</t>
+          <t>7878</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4988,32 +4988,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>8723</t>
+          <t>8739</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>4872</t>
+          <t>4744</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>15132</t>
+          <t>15895</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>1329</t>
+          <t>2761</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>7011</t>
+          <t>9378</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>1329</t>
+          <t>2761</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>6535</t>
+          <t>9717</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>715</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3802</t>
+          <t>4276</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5204,7 +5204,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>715</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
@@ -5224,7 +5224,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>2687</t>
+          <t>3623</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,33%</t>
         </is>
       </c>
     </row>
@@ -5257,22 +5257,22 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>3761</t>
+          <t>3790</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1065</t>
+          <t>1105</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>9714</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5292,32 +5292,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>4210</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1882</t>
+          <t>1722</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>9333</t>
+          <t>9986</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5327,32 +5327,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>7971</t>
+          <t>8860</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>3983</t>
+          <t>4483</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>14340</t>
+          <t>16399</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -5370,32 +5370,32 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>5544</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>1836</t>
+          <t>1786</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>12986</t>
+          <t>12050</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5405,32 +5405,32 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>6334</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2986</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>13419</t>
+          <t>13117</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5440,22 +5440,22 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>11818</t>
+          <t>11690</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>6003</t>
+          <t>6523</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>19916</t>
+          <t>19213</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -5483,32 +5483,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>6941</t>
+          <t>8563</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>3012</t>
+          <t>3574</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>13108</t>
+          <t>16042</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5518,22 +5518,22 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>6683</t>
+          <t>6899</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>2921</t>
+          <t>3173</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>15940</t>
+          <t>13875</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5553,32 +5553,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>13624</t>
+          <t>15462</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>7911</t>
+          <t>8438</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>22824</t>
+          <t>25968</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -5596,32 +5596,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>3185</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>1110</t>
+          <t>714</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>8385</t>
+          <t>7605</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5631,32 +5631,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>3126</t>
+          <t>3191</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>7226</t>
+          <t>7643</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5666,32 +5666,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>6311</t>
+          <t>6380</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>2941</t>
+          <t>2964</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>11587</t>
+          <t>12141</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -5709,22 +5709,22 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>12724</t>
+          <t>10964</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>5396</t>
+          <t>5824</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>35012</t>
+          <t>24604</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5744,32 +5744,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>10464</t>
+          <t>12626</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>6354</t>
+          <t>7200</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>16916</t>
+          <t>19005</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5779,22 +5779,22 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>23188</t>
+          <t>23590</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>14918</t>
+          <t>16124</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>45688</t>
+          <t>36935</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
@@ -5804,7 +5804,7 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -5822,32 +5822,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>59010</t>
+          <t>61609</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>46498</t>
+          <t>48266</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>75244</t>
+          <t>77442</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5857,32 +5857,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>57021</t>
+          <t>61905</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>46371</t>
+          <t>50652</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>69832</t>
+          <t>76332</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5892,32 +5892,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>116031</t>
+          <t>123515</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>100631</t>
+          <t>104620</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>134594</t>
+          <t>141777</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>12,98%</t>
         </is>
       </c>
     </row>
@@ -5935,32 +5935,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>377301</t>
+          <t>410950</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>355807</t>
+          <t>392397</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>394792</t>
+          <t>430566</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5970,32 +5970,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>436440</t>
+          <t>478282</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>419371</t>
+          <t>461708</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>450684</t>
+          <t>492459</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6005,32 +6005,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>813742</t>
+          <t>889232</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>788881</t>
+          <t>865174</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>835607</t>
+          <t>911658</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>81,41%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>79,2%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>83,46%</t>
         </is>
       </c>
     </row>
@@ -6048,17 +6048,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>475202</t>
+          <t>512433</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>475202</t>
+          <t>512433</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>475202</t>
+          <t>512433</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6083,17 +6083,17 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>529558</t>
+          <t>579920</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>529558</t>
+          <t>579920</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>529558</t>
+          <t>579920</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6118,17 +6118,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>1004761</t>
+          <t>1092353</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>1004761</t>
+          <t>1092353</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>1004761</t>
+          <t>1092353</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6165,32 +6165,32 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>9066</t>
+          <t>11575</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>3738</t>
+          <t>5073</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>16767</t>
+          <t>20999</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6200,32 +6200,32 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>7360</t>
+          <t>7616</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>3449</t>
+          <t>3896</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>14189</t>
+          <t>14723</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6235,32 +6235,32 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>16426</t>
+          <t>19190</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>9608</t>
+          <t>11732</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>26465</t>
+          <t>30374</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -6278,32 +6278,32 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>12961</t>
+          <t>15512</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>6786</t>
+          <t>9012</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>22049</t>
+          <t>26548</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6313,32 +6313,32 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>9284</t>
+          <t>10341</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>4928</t>
+          <t>5772</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>16392</t>
+          <t>17680</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6348,32 +6348,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>22245</t>
+          <t>25853</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>14481</t>
+          <t>16777</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>33378</t>
+          <t>37994</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -6391,32 +6391,32 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>2456</t>
+          <t>3949</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>1115</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>8988</t>
+          <t>11364</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>0,01%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6426,32 +6426,32 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>3004</t>
+          <t>2597</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>695</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>10337</t>
+          <t>7767</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6461,32 +6461,32 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>5460</t>
+          <t>6546</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>1856</t>
+          <t>2341</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>12607</t>
+          <t>14090</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,39%</t>
         </is>
       </c>
     </row>
@@ -6539,32 +6539,32 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>2482</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>717</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>7724</t>
+          <t>7159</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6574,17 +6574,17 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>2482</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>718</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>6895</t>
+          <t>7369</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
     </row>
@@ -6617,67 +6617,67 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>14696</t>
+          <t>15378</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>8190</t>
+          <t>8603</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>24974</t>
+          <t>25418</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>16609</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>10283</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>25735</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
           <t>0,89%</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>14436</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="inlineStr">
-        <is>
-          <t>8655</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr">
-        <is>
-          <t>22806</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6687,32 +6687,32 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>29132</t>
+          <t>31987</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>19392</t>
+          <t>22236</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>41985</t>
+          <t>44226</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -6730,32 +6730,32 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>20097</t>
+          <t>19203</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>11207</t>
+          <t>10926</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>39914</t>
+          <t>35328</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6765,32 +6765,32 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>10211</t>
+          <t>10439</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>5070</t>
+          <t>5816</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>17883</t>
+          <t>17208</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6800,32 +6800,32 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>30308</t>
+          <t>29642</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>19808</t>
+          <t>20047</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>51708</t>
+          <t>45832</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -6843,32 +6843,32 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>30922</t>
+          <t>34281</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>18591</t>
+          <t>22755</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>50759</t>
+          <t>54062</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6878,22 +6878,22 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>74209</t>
+          <t>45511</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>35369</t>
+          <t>34259</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>188811</t>
+          <t>62424</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
@@ -6903,7 +6903,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6913,32 +6913,32 @@
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>105131</t>
+          <t>79792</t>
         </is>
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>65088</t>
+          <t>61259</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>259745</t>
+          <t>105655</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -6956,32 +6956,32 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>33180</t>
+          <t>34404</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>21897</t>
+          <t>23169</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>46900</t>
+          <t>51769</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -6991,32 +6991,32 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>17005</t>
+          <t>18881</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>10040</t>
+          <t>13217</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>24483</t>
+          <t>26971</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7026,32 +7026,32 @@
       </c>
       <c r="R59" s="2" t="inlineStr">
         <is>
-          <t>50184</t>
+          <t>53286</t>
         </is>
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>37468</t>
+          <t>40691</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>67960</t>
+          <t>71851</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -7069,32 +7069,32 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>92646</t>
+          <t>99664</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>71986</t>
+          <t>76745</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>121176</t>
+          <t>125156</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7104,32 +7104,32 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>73667</t>
+          <t>87540</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>52719</t>
+          <t>73669</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>90402</t>
+          <t>104752</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7139,32 +7139,32 @@
       </c>
       <c r="R60" s="2" t="inlineStr">
         <is>
-          <t>166314</t>
+          <t>187204</t>
         </is>
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>130783</t>
+          <t>161253</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>200021</t>
+          <t>217540</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -7182,32 +7182,32 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>188942</t>
+          <t>201737</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>164745</t>
+          <t>175067</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>218285</t>
+          <t>228300</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7217,32 +7217,32 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>181557</t>
+          <t>197074</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>129541</t>
+          <t>175469</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>213533</t>
+          <t>223696</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7252,32 +7252,32 @@
       </c>
       <c r="R61" s="2" t="inlineStr">
         <is>
-          <t>370499</t>
+          <t>398811</t>
         </is>
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>303378</t>
+          <t>364533</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>412655</t>
+          <t>435574</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,91%</t>
         </is>
       </c>
     </row>
@@ -7295,32 +7295,32 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>1250069</t>
+          <t>1365372</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>1204150</t>
+          <t>1320587</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>1291266</t>
+          <t>1407764</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>75,81%</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>73,32%</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>78,02%</t>
+          <t>78,16%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7330,32 +7330,32 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>1514580</t>
+          <t>1457263</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>1435429</t>
+          <t>1424488</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>1623612</t>
+          <t>1486307</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>78,5%</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>76,73%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7365,32 +7365,32 @@
       </c>
       <c r="R62" s="2" t="inlineStr">
         <is>
-          <t>2764650</t>
+          <t>2822634</t>
         </is>
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>2672528</t>
+          <t>2772875</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>2904034</t>
+          <t>2873058</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>77,17%</t>
         </is>
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>75,81%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>78,55%</t>
         </is>
       </c>
     </row>
@@ -7408,17 +7408,17 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>1655035</t>
+          <t>1801075</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>1655035</t>
+          <t>1801075</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>1655035</t>
+          <t>1801075</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>1907795</t>
+          <t>1856481</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>1907795</t>
+          <t>1856481</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>1907795</t>
+          <t>1856481</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7478,17 +7478,17 @@
       </c>
       <c r="R63" s="2" t="inlineStr">
         <is>
-          <t>3562831</t>
+          <t>3657555</t>
         </is>
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>3562831</t>
+          <t>3657555</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>3562831</t>
+          <t>3657555</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">

--- a/data/trans_orig/RUIDO_1-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/RUIDO_1-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según lo que estaría dispuesta a pagar al año para que la administración pública ponga en marcha actuaciones (+++) en su municipio/ciudad (o lugar de residencia) que haga reducir la contaminación del ruido en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Población según lo que estaría dispuesta a pagar al año para que la administración pública ponga en marcha actuaciones en su municipio/ciudad (o lugar de residencia) que haga reducir la contaminación del ruido en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
